--- a/artfynd/A 42849-2025 artfynd.xlsx
+++ b/artfynd/A 42849-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130142106</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>130142093</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42849-2025 artfynd.xlsx
+++ b/artfynd/A 42849-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130142106</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>130142093</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42849-2025 artfynd.xlsx
+++ b/artfynd/A 42849-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130142106</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>130142093</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
